--- a/экспертные системы/лаб4/СИМВОЛ.xlsx
+++ b/экспертные системы/лаб4/СИМВОЛ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavel\Documents\GitHub\AI_LABS\экспертные системы\лаб4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavel\Documents\GitHub\AI_LABS1\экспертные системы\лаб4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BE2B3F-6F6A-42D3-8F3A-A7198442335E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7172AFE-67D8-415C-8A2C-7C43E8BACD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -338,9 +338,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1">
         <v>1</v>
       </c>
@@ -351,7 +351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -362,7 +362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -370,10 +370,10 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>0</v>
       </c>
@@ -384,15 +384,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
